--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13.11</v>
+        <v>16.53</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="E2">
-        <v>12.42</v>
+        <v>14.28</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15.21</v>
+        <v>7.06</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
       <c r="D3">
-        <v>216.5</v>
+        <v>95.5</v>
       </c>
       <c r="E3">
-        <v>12.56</v>
+        <v>6.53</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12.33</v>
+        <v>16.15</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="E2">
-        <v>12.43</v>
+        <v>14.33</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15.09</v>
+        <v>6.84</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>216.5</v>
+        <v>95.5</v>
       </c>
       <c r="E3">
-        <v>12.59</v>
+        <v>6.54</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>19.5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.53</v>
+        <v>18.9</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E2">
-        <v>14.28</v>
+        <v>16.99</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.06</v>
+        <v>15.27</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>95.5</v>
+        <v>251.17</v>
       </c>
       <c r="E3">
-        <v>6.53</v>
+        <v>14.6</v>
       </c>
       <c r="F3">
-        <v>5.5</v>
+        <v>11.02</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>6.01</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>20.03</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.15</v>
+        <v>18.46</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E2">
-        <v>14.33</v>
+        <v>17.03</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.84</v>
+        <v>14.81</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>95.5</v>
+        <v>251.17</v>
       </c>
       <c r="E3">
-        <v>6.54</v>
+        <v>14.61</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>11.02</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>5.01</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>19.03</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw.xlsx
@@ -402,7 +402,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18.9</v>
+        <v>19.59</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -411,16 +411,16 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>16.99</v>
+        <v>18.23</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>14.05</v>
       </c>
       <c r="G2">
         <v>8</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -428,16 +428,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15.27</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>251.17</v>
+        <v>174.08</v>
       </c>
       <c r="E3">
-        <v>14.6</v>
+        <v>14.42</v>
       </c>
       <c r="F3">
         <v>11.02</v>
@@ -446,7 +446,7 @@
         <v>6.01</v>
       </c>
       <c r="H3">
-        <v>20.03</v>
+        <v>19.03</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>18.46</v>
+        <v>18.9</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -515,16 +515,16 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>17.03</v>
+        <v>18.26</v>
       </c>
       <c r="F2">
         <v>14</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="3">
@@ -532,16 +532,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14.81</v>
+        <v>14.51</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>251.17</v>
+        <v>174.08</v>
       </c>
       <c r="E3">
-        <v>14.61</v>
+        <v>14.43</v>
       </c>
       <c r="F3">
         <v>11.02</v>
